--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalerInstInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalerInstInfo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BS3.0feature-3.0.4运营\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="总部或分支机构信息" sheetId="3" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -22,39 +22,34 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>销售机构代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>总部或分支机构编码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>总部或分支机构名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>机构层级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>备注</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -66,7 +61,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -75,7 +70,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -109,12 +110,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -420,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14.125" bestFit="1" customWidth="1"/>
@@ -446,13 +453,26 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="2">
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>"01 总行或总部 ,02 分支行或分部"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalerInstInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalerInstInfo.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>销售机构代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -34,10 +34,6 @@
   </si>
   <si>
     <t>机构层级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -427,16 +423,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14.125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="20.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -449,23 +444,18 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
